--- a/artfynd/A 44885-2025 artfynd.xlsx
+++ b/artfynd/A 44885-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,51 +794,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>54927515</v>
+        <v>137151993</v>
       </c>
       <c r="B3" t="n">
-        <v>111175</v>
+        <v>100922</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219677</v>
+        <v>783</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Västeralvar, Öl</t>
+          <t>Ebberskog, Öl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>622733</v>
+        <v>622588</v>
       </c>
       <c r="R3" t="n">
-        <v>6356768</v>
+        <v>6356440</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,12 +859,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-08-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-08-22</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,72 +879,65 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson, Bengt Westman, Pontus Axén</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54927515</t>
+          <t>https://artportalen.se/Sighting/137151993</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>54927519</v>
+        <v>137152012</v>
       </c>
       <c r="B4" t="n">
-        <v>99096</v>
+        <v>75550</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>1460</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Västeralvar, Öl</t>
+          <t>Ebberskog, Öl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>622729</v>
+        <v>622575</v>
       </c>
       <c r="R4" t="n">
-        <v>6356761</v>
+        <v>6356353</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,12 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2015-08-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2015-08-22</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,35 +977,36 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Ek</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson, Bengt Westman, Pontus Axén</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54927519</t>
+          <t>https://artportalen.se/Sighting/137152012</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>54927482</v>
+        <v>54927515</v>
       </c>
       <c r="B5" t="n">
-        <v>99120</v>
+        <v>111175</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1023,21 +1014,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219811</v>
+        <v>219677</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1050,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>622748</v>
+        <v>622733</v>
       </c>
       <c r="R5" t="n">
-        <v>6356814</v>
+        <v>6356768</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1115,38 +1106,38 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54927482</t>
+          <t>https://artportalen.se/Sighting/54927515</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>54927523</v>
+        <v>54927519</v>
       </c>
       <c r="B6" t="n">
-        <v>106812</v>
+        <v>99096</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220785</v>
+        <v>219798</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1159,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>622722</v>
+        <v>622729</v>
       </c>
       <c r="R6" t="n">
-        <v>6356747</v>
+        <v>6356761</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1224,16 +1215,16 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54927523</t>
+          <t>https://artportalen.se/Sighting/54927519</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>54927517</v>
+        <v>54927482</v>
       </c>
       <c r="B7" t="n">
-        <v>106328</v>
+        <v>99120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,21 +1232,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221423</v>
+        <v>219811</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1268,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>622729</v>
+        <v>622748</v>
       </c>
       <c r="R7" t="n">
-        <v>6356761</v>
+        <v>6356814</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1315,11 +1306,6 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>nyröjd skogsmark</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
@@ -1338,38 +1324,38 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54927517</t>
+          <t>https://artportalen.se/Sighting/54927482</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>54927502</v>
+        <v>54927523</v>
       </c>
       <c r="B8" t="n">
-        <v>101325</v>
+        <v>106812</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>220785</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>622738</v>
+        <v>622722</v>
       </c>
       <c r="R8" t="n">
-        <v>6356784</v>
+        <v>6356747</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1447,38 +1433,38 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54927502</t>
+          <t>https://artportalen.se/Sighting/54927523</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>54927528</v>
+        <v>54927517</v>
       </c>
       <c r="B9" t="n">
-        <v>103402</v>
+        <v>106328</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223246</v>
+        <v>221423</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1491,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>622711</v>
+        <v>622729</v>
       </c>
       <c r="R9" t="n">
-        <v>6356736</v>
+        <v>6356761</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1538,6 +1524,11 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>nyröjd skogsmark</t>
+        </is>
+      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
@@ -1556,36 +1547,40 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54927528</t>
+          <t>https://artportalen.se/Sighting/54927517</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>54927491</v>
+        <v>54927502</v>
       </c>
       <c r="B10" t="n">
-        <v>104640</v>
+        <v>101325</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>224416</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -1596,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>622748</v>
+        <v>622738</v>
       </c>
       <c r="R10" t="n">
-        <v>6356814</v>
+        <v>6356784</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1660,6 +1655,220 @@
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54927502</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>54927528</v>
+      </c>
+      <c r="B11" t="n">
+        <v>103402</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Västeralvar, Öl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>622711</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6356736</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2015-08-22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2015-08-22</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson, Bengt Westman, Pontus Axén</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54927528</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>54927491</v>
+      </c>
+      <c r="B12" t="n">
+        <v>104640</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Västeralvar, Öl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>622748</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6356814</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2015-08-22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2015-08-22</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson, Bengt Westman, Pontus Axén</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/54927491</t>
         </is>
@@ -1676,6 +1885,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44885-2025 artfynd.xlsx
+++ b/artfynd/A 44885-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>137151993</v>
       </c>
       <c r="B3" t="n">
-        <v>100922</v>
+        <v>100924</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44885-2025 artfynd.xlsx
+++ b/artfynd/A 44885-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>137151993</v>
       </c>
       <c r="B3" t="n">
-        <v>100924</v>
+        <v>100926</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44885-2025 artfynd.xlsx
+++ b/artfynd/A 44885-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>137151993</v>
       </c>
       <c r="B3" t="n">
-        <v>100926</v>
+        <v>100939</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>137152012</v>
       </c>
       <c r="B4" t="n">
-        <v>75550</v>
+        <v>75563</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44885-2025 artfynd.xlsx
+++ b/artfynd/A 44885-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>137151993</v>
       </c>
       <c r="B3" t="n">
-        <v>100939</v>
+        <v>100941</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>137152012</v>
       </c>
       <c r="B4" t="n">
-        <v>75563</v>
+        <v>75565</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44885-2025 artfynd.xlsx
+++ b/artfynd/A 44885-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>137151993</v>
       </c>
       <c r="B3" t="n">
-        <v>100941</v>
+        <v>100944</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44885-2025 artfynd.xlsx
+++ b/artfynd/A 44885-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>137151993</v>
       </c>
       <c r="B3" t="n">
-        <v>100944</v>
+        <v>100954</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>137152012</v>
       </c>
       <c r="B4" t="n">
-        <v>75565</v>
+        <v>75575</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44885-2025 artfynd.xlsx
+++ b/artfynd/A 44885-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>137151993</v>
       </c>
       <c r="B3" t="n">
-        <v>100954</v>
+        <v>100955</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44885-2025 artfynd.xlsx
+++ b/artfynd/A 44885-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>137151993</v>
       </c>
       <c r="B3" t="n">
-        <v>100955</v>
+        <v>100960</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>137152012</v>
       </c>
       <c r="B4" t="n">
-        <v>75575</v>
+        <v>75578</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44885-2025 artfynd.xlsx
+++ b/artfynd/A 44885-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>137151993</v>
       </c>
       <c r="B3" t="n">
-        <v>100960</v>
+        <v>100963</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44885-2025 artfynd.xlsx
+++ b/artfynd/A 44885-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>137151993</v>
       </c>
       <c r="B3" t="n">
-        <v>100963</v>
+        <v>100969</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>137152012</v>
       </c>
       <c r="B4" t="n">
-        <v>75578</v>
+        <v>75583</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44885-2025 artfynd.xlsx
+++ b/artfynd/A 44885-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>137151993</v>
       </c>
       <c r="B3" t="n">
-        <v>100969</v>
+        <v>100981</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>137152012</v>
       </c>
       <c r="B4" t="n">
-        <v>75583</v>
+        <v>75594</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44885-2025 artfynd.xlsx
+++ b/artfynd/A 44885-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>137151993</v>
       </c>
       <c r="B3" t="n">
-        <v>100981</v>
+        <v>100982</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44885-2025 artfynd.xlsx
+++ b/artfynd/A 44885-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>137151993</v>
       </c>
       <c r="B3" t="n">
-        <v>100982</v>
+        <v>100985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44885-2025 artfynd.xlsx
+++ b/artfynd/A 44885-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>137151993</v>
       </c>
       <c r="B3" t="n">
-        <v>100985</v>
+        <v>100989</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>137152012</v>
       </c>
       <c r="B4" t="n">
-        <v>75594</v>
+        <v>75598</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44885-2025 artfynd.xlsx
+++ b/artfynd/A 44885-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>137151993</v>
       </c>
       <c r="B3" t="n">
-        <v>100989</v>
+        <v>100991</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
